--- a/results/job_matches_2026-07-06.xlsx
+++ b/results/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,68 +468,173 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ciklum</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Engineer II, Data Engineering</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Magnite</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Broomfield, CO, US USA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D6" t="n">
         <v>10.4</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>RDS, Hadoop, Spark, Scala, Kafka, ETL, Jenkins, AKS, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f56661e330370a6d</t>
         </is>

--- a/results/job_matches_2026-07-06.xlsx
+++ b/results/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,52 +591,297 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quincy, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior ML/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CareScout</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JPS Tech Solutions pvt ltd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Engineer II, Data Engineering</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Magnite</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Broomfield, CO, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D11" t="n">
         <v>10.4</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>RDS, Hadoop, Spark, Scala, Kafka, ETL, Jenkins, AKS, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f56661e330370a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer, Associate</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Infor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0971a287a1cb34b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CareScout</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-06.xlsx
+++ b/results/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb05c2c61999715</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Technology</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
+          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
+          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Almont, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,110 +776,355 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Engineer II, Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, ETL, Jenkins, AKS, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56661e330370a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0971a287a1cb34b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Senior ML/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CareScout</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JPS Tech Solutions pvt ltd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Functional Netsuite Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Koya Consulting</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Garden Grove, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Engineer II, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Magnite</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, ETL, Jenkins, AKS, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f56661e330370a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IT Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Qarbon Aerospace</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Red Oak, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer, Associate</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Infor</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0971a287a1cb34b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>CareScout</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D20" t="n">
         <v>10.4</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
         </is>

--- a/results/job_matches_2026-07-06.xlsx
+++ b/results/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Technology</t>
+          <t>Senior Data Engineer (P1692)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
+          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Technology</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
+          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
         </is>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Almont, CO, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
+          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Almont, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
+          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer II, Data Engineering</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, ETL, Jenkins, AKS, Jenkins, Git</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56661e330370a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>JPS Tech Solutions pvt ltd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,75 +1056,495 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0971a287a1cb34b9</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Healthcare Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nephrocare Dialysis, LLC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Functional Netsuite Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Koya Consulting</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Garden Grove, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Flexjet, LLC.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Canary Technologies</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, ELT, CI/CD, GitHub Actions, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4fd8be2ac2acbae</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Associate</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Charter Schools USA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Senior Data Engineer</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IT Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Qarbon Aerospace</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Red Oak, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Flexjet, LLC.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>CareScout</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D32" t="n">
         <v>10.4</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
         </is>

--- a/results/job_matches_2026-07-06.xlsx
+++ b/results/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1692)</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
+          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Technology</t>
+          <t>Senior Data Engineer (P1692)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
+          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
+          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
+          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
+          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Almont, CO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Almont, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=63633a8200979a09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>JPS Tech Solutions pvt ltd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
         </is>
       </c>
     </row>
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Healthcare Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Nephrocare Dialysis, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Functional Netsuite Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Canary Technologies</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ELT, CI/CD, GitHub Actions, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd8be2ac2acbae</t>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=6266f795f6f70349</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Cloud Solutions Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Charter Schools USA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,192 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IT Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Qarbon Aerospace</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Red Oak, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Flexjet, LLC.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CareScout</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=660813ceffa3da5b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-06.xlsx
+++ b/results/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer (Bilingual Mandarin Required)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb05c2c61999715</t>
+          <t>https://www.indeed.com/viewjob?jk=83640374dcc1134d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer, Business Intelligence Analyst</t>
+          <t>Data Engineer (Bilingual Mandarin Required)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bf10f975373c2da2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (P1692)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb05c2c61999715</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Technology</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
+          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (P1692)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>Azure, Databricks, Delta Live Tables, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
+          <t>https://www.indeed.com/viewjob?jk=22049a363074e096</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Technology</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
+          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3be0a56ac2778b38</t>
         </is>
       </c>
     </row>
@@ -718,20 +718,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, HBase, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b690f84b839f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Snowflake, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1d05903802863d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=ebaeeabafbe5553f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Almont, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c36cf1a20fa03687</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Azure Cosmos DB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
+          <t>https://www.indeed.com/viewjob?jk=104030bc904b311c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Almont, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=01bd0155c82472f6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=f573c104948a88be</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63633a8200979a09</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Senior Technologist - Institutional Operations Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf6b377d6b97198</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Analytics Analyst</t>
+          <t>Senior Software Engineer – Cloud-Native Applications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, DynamoDB, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
+          <t>https://www.indeed.com/viewjob?jk=61eba61db8d1d33f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPS Tech Solutions pvt ltd</t>
+          <t>Grid Elevated</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
+          <t>https://www.indeed.com/viewjob?jk=618a1dbe7d6ef58d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
+          <t>https://www.indeed.com/viewjob?jk=63633a8200979a09</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healthcare Software Engineer</t>
+          <t>Senior Embedded Software &amp; DevOps Engineer – Powertrain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nephrocare Dialysis, LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0c89d04dc203d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Functional Netsuite Developer</t>
+          <t>Senior Guidewire Developer (PolicyCenter)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Koya Consulting</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b36b3a62dfe376d5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>JPS Tech Solutions pvt ltd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeca00e004c5b061</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer, Clinical Operations</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6266f795f6f70349</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a0103edeceecc7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Solutions Associate</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Charter Schools USA</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Snowflake, Oracle, Power BI, CI/CD, Jenkins, Maven, AKS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=747068d5750d5c05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Healthcare Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nephrocare Dialysis, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=35a391cf99eaaca4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT Business Intelligence Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qarbon Aerospace</t>
+          <t>Synapse Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Red Oak, TX, US USA</t>
+          <t>Skokie, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=38a6c99045779145</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Functional Netsuite Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+          <t>https://www.indeed.com/viewjob?jk=b420712f769081b2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,77 +1651,567 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, ETL, ELT, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=101ca2c1e32226ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faae996969c3b654</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb292e68230c43cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Java Angular Developer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2513c2da5e1dcae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6266f795f6f70349</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Technical Product Owner - Snowflake</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Associated Bank</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, ETL, ELT, DataOps, MLOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee15581de1910c63</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer II, Assoc.Dir.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FHLBank San Francisco</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Azure, Oracle, Data Modeling, ETL, ELT, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=959dfa60ea3aa32b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Associate</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Charter Schools USA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Blob Storage, GCP, Scala, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09dfaa59c130fbb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Spark, PySpark, Scala, Data Modeling, Kimball, Fact Tables, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3665a915e740dcb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IT Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Qarbon Aerospace</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Red Oak, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Medallion Architecture, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=753cae0999113ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f427c7860949a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CareScout</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Amplify</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D50" t="n">
         <v>10.4</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=660813ceffa3da5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Flexjet, LLC.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
         </is>
       </c>
     </row>
